--- a/inventories/baseline/lci-Salar-de-Centenario.xlsx
+++ b/inventories/baseline/lci-Salar-de-Centenario.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://leidenuniv1-my.sharepoint.com/personal/istrateir_vuw_leidenuniv_nl/Documents/Research/lithium-brine-prospective-LCA/inventories/raw/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_25C98721036BADE3A07448B1D5C023FE43DC5CE0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77EDAA82-8C54-46D8-AF62-EF6D5CE77169}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Salar de Centenario" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -235,8 +229,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,21 +276,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -334,7 +320,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -368,7 +354,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -403,10 +388,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -579,14 +563,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F276"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="34.5703125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -594,7 +575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -602,7 +583,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -610,7 +591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -618,7 +599,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -626,7 +607,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -634,7 +615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -642,7 +623,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -650,12 +631,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -675,12 +656,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12">
-        <v>2.5000000000000001E-4</v>
+        <v>0.00025</v>
       </c>
       <c r="D12" t="s">
         <v>16</v>
@@ -692,12 +673,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>19</v>
       </c>
       <c r="B13">
-        <v>1.25E-3</v>
+        <v>0.00125</v>
       </c>
       <c r="D13" t="s">
         <v>16</v>
@@ -709,7 +690,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -726,12 +707,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>22</v>
       </c>
       <c r="B15">
-        <v>7.2059999999999997E-3</v>
+        <v>0.007206</v>
       </c>
       <c r="C15" t="s">
         <v>23</v>
@@ -743,7 +724,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
         <v>2</v>
       </c>
@@ -751,7 +732,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -759,7 +740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -767,7 +748,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -775,7 +756,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -783,7 +764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -791,7 +772,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -799,12 +780,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -824,7 +805,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -841,7 +822,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -858,7 +839,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -875,12 +856,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>15</v>
       </c>
       <c r="B29">
-        <v>1.111111111111111E-4</v>
+        <v>0.0001111111111111111</v>
       </c>
       <c r="D29" t="s">
         <v>16</v>
@@ -892,7 +873,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>26</v>
       </c>
@@ -909,7 +890,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -926,12 +907,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>33</v>
       </c>
       <c r="B32">
-        <v>1.1111111111111109</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="C32" t="s">
         <v>1</v>
@@ -943,12 +924,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>34</v>
       </c>
       <c r="B33">
-        <v>-1.111111111111111E-4</v>
+        <v>-0.0001111111111111111</v>
       </c>
       <c r="C33" t="s">
         <v>1</v>
@@ -960,7 +941,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6">
       <c r="A35" s="1" t="s">
         <v>2</v>
       </c>
@@ -968,7 +949,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -976,7 +957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -984,7 +965,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -992,7 +973,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>7</v>
       </c>
@@ -1000,7 +981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>8</v>
       </c>
@@ -1008,7 +989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>10</v>
       </c>
@@ -1016,12 +997,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6">
       <c r="A42" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>13</v>
       </c>
@@ -1041,7 +1022,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>35</v>
       </c>
@@ -1058,12 +1039,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>3</v>
       </c>
       <c r="B45">
-        <v>7.4446913664903649E-2</v>
+        <v>0.07444691366490365</v>
       </c>
       <c r="C45" t="s">
         <v>1</v>
@@ -1075,7 +1056,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>36</v>
       </c>
@@ -1092,7 +1073,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>37</v>
       </c>
@@ -1109,12 +1090,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>39</v>
       </c>
       <c r="B48">
-        <v>6.333333333333333E-4</v>
+        <v>0.0006333333333333333</v>
       </c>
       <c r="C48" t="s">
         <v>40</v>
@@ -1126,12 +1107,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>22</v>
       </c>
       <c r="B49">
-        <v>1.5261549061760379E-3</v>
+        <v>0.001526154906176038</v>
       </c>
       <c r="C49" t="s">
         <v>23</v>
@@ -1143,12 +1124,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>41</v>
       </c>
       <c r="B50">
-        <v>-2.9999999999999997E-4</v>
+        <v>-0.0003</v>
       </c>
       <c r="C50" t="s">
         <v>40</v>
@@ -1160,7 +1141,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6">
       <c r="A52" s="1" t="s">
         <v>2</v>
       </c>
@@ -1168,7 +1149,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -1176,7 +1157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -1184,7 +1165,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1192,7 +1173,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>7</v>
       </c>
@@ -1200,7 +1181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>8</v>
       </c>
@@ -1208,7 +1189,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>10</v>
       </c>
@@ -1216,12 +1197,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6">
       <c r="A59" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>13</v>
       </c>
@@ -1241,7 +1222,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>43</v>
       </c>
@@ -1258,7 +1239,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>42</v>
       </c>
@@ -1275,7 +1256,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>44</v>
       </c>
@@ -1292,12 +1273,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>37</v>
       </c>
       <c r="B64">
-        <v>0.89443364037895146</v>
+        <v>0.8944336403789515</v>
       </c>
       <c r="C64" t="s">
         <v>1</v>
@@ -1309,7 +1290,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6">
       <c r="A66" s="1" t="s">
         <v>2</v>
       </c>
@@ -1317,7 +1298,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>4</v>
       </c>
@@ -1325,7 +1306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>5</v>
       </c>
@@ -1333,7 +1314,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -1341,7 +1322,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>7</v>
       </c>
@@ -1349,7 +1330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
         <v>8</v>
       </c>
@@ -1357,7 +1338,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
         <v>10</v>
       </c>
@@ -1365,12 +1346,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6">
       <c r="A73" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>13</v>
       </c>
@@ -1390,7 +1371,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>45</v>
       </c>
@@ -1407,12 +1388,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>3</v>
       </c>
       <c r="B76">
-        <v>2.3404910807260058E-2</v>
+        <v>0.02340491080726006</v>
       </c>
       <c r="C76" t="s">
         <v>1</v>
@@ -1424,12 +1405,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>26</v>
       </c>
       <c r="B77">
-        <v>0.97074386149092495</v>
+        <v>0.970743861490925</v>
       </c>
       <c r="C77" t="s">
         <v>1</v>
@@ -1441,12 +1422,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
         <v>37</v>
       </c>
       <c r="B78">
-        <v>0.26624537354409339</v>
+        <v>0.2662453735440934</v>
       </c>
       <c r="C78" t="s">
         <v>1</v>
@@ -1458,12 +1439,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
         <v>46</v>
       </c>
       <c r="B79">
-        <v>5.8512277018150146E-3</v>
+        <v>0.005851227701815015</v>
       </c>
       <c r="C79" t="s">
         <v>47</v>
@@ -1475,7 +1456,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6">
       <c r="A81" s="1" t="s">
         <v>2</v>
       </c>
@@ -1483,7 +1464,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>4</v>
       </c>
@@ -1491,7 +1472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>5</v>
       </c>
@@ -1499,7 +1480,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>6</v>
       </c>
@@ -1507,7 +1488,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
         <v>7</v>
       </c>
@@ -1515,7 +1496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
         <v>8</v>
       </c>
@@ -1523,7 +1504,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
         <v>10</v>
       </c>
@@ -1531,12 +1512,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6">
       <c r="A88" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>13</v>
       </c>
@@ -1556,7 +1537,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>48</v>
       </c>
@@ -1573,12 +1554,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>3</v>
       </c>
       <c r="B91">
-        <v>4.0187828572855779E-2</v>
+        <v>0.04018782857285578</v>
       </c>
       <c r="C91" t="s">
         <v>1</v>
@@ -1590,12 +1571,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
         <v>49</v>
       </c>
       <c r="B92">
-        <v>0.94976521428393024</v>
+        <v>0.9497652142839302</v>
       </c>
       <c r="C92" t="s">
         <v>1</v>
@@ -1607,12 +1588,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
         <v>37</v>
       </c>
       <c r="B93">
-        <v>0.17774062929669121</v>
+        <v>0.1777406292966912</v>
       </c>
       <c r="C93" t="s">
         <v>1</v>
@@ -1624,12 +1605,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
         <v>46</v>
       </c>
       <c r="B94">
-        <v>1.0046957143213939E-2</v>
+        <v>0.01004695714321394</v>
       </c>
       <c r="C94" t="s">
         <v>47</v>
@@ -1641,7 +1622,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6">
       <c r="A96" s="1" t="s">
         <v>2</v>
       </c>
@@ -1649,7 +1630,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
         <v>4</v>
       </c>
@@ -1657,7 +1638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
         <v>5</v>
       </c>
@@ -1665,7 +1646,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
         <v>6</v>
       </c>
@@ -1673,7 +1654,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
         <v>7</v>
       </c>
@@ -1681,7 +1662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
         <v>8</v>
       </c>
@@ -1689,7 +1670,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
         <v>10</v>
       </c>
@@ -1697,12 +1678,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6">
       <c r="A103" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
         <v>13</v>
       </c>
@@ -1722,7 +1703,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
         <v>36</v>
       </c>
@@ -1739,12 +1720,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
         <v>48</v>
       </c>
       <c r="B106">
-        <v>0.99634041458014255</v>
+        <v>0.9963404145801426</v>
       </c>
       <c r="C106" t="s">
         <v>1</v>
@@ -1756,12 +1737,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
         <v>50</v>
       </c>
       <c r="B107">
-        <v>3.6595854198574491E-3</v>
+        <v>0.003659585419857449</v>
       </c>
       <c r="C107" t="s">
         <v>40</v>
@@ -1773,7 +1754,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6">
       <c r="A109" s="1" t="s">
         <v>2</v>
       </c>
@@ -1781,7 +1762,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6">
       <c r="A110" t="s">
         <v>4</v>
       </c>
@@ -1789,7 +1770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6">
       <c r="A111" t="s">
         <v>5</v>
       </c>
@@ -1797,7 +1778,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6">
       <c r="A112" t="s">
         <v>6</v>
       </c>
@@ -1805,7 +1786,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>7</v>
       </c>
@@ -1813,7 +1794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>8</v>
       </c>
@@ -1821,7 +1802,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
         <v>10</v>
       </c>
@@ -1829,12 +1810,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6">
       <c r="A116" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
         <v>13</v>
       </c>
@@ -1854,7 +1835,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
         <v>51</v>
       </c>
@@ -1871,12 +1852,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
         <v>42</v>
       </c>
       <c r="B119">
-        <v>7.7164002898357591</v>
+        <v>7.716400289835759</v>
       </c>
       <c r="C119" t="s">
         <v>1</v>
@@ -1888,12 +1869,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
         <v>22</v>
       </c>
       <c r="B120">
-        <v>8.2223937514643332E-3</v>
+        <v>0.008222393751464333</v>
       </c>
       <c r="C120" t="s">
         <v>23</v>
@@ -1905,12 +1886,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
         <v>34</v>
       </c>
       <c r="B121">
-        <v>-6.7164002898357587E-3</v>
+        <v>-0.006716400289835759</v>
       </c>
       <c r="C121" t="s">
         <v>1</v>
@@ -1922,7 +1903,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6">
       <c r="A123" s="1" t="s">
         <v>2</v>
       </c>
@@ -1930,7 +1911,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
         <v>4</v>
       </c>
@@ -1938,7 +1919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
         <v>5</v>
       </c>
@@ -1946,7 +1927,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
         <v>6</v>
       </c>
@@ -1954,7 +1935,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
         <v>7</v>
       </c>
@@ -1962,7 +1943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
         <v>8</v>
       </c>
@@ -1970,7 +1951,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6">
       <c r="A129" t="s">
         <v>10</v>
       </c>
@@ -1978,12 +1959,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6">
       <c r="A130" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6">
       <c r="A131" t="s">
         <v>13</v>
       </c>
@@ -2003,7 +1984,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6">
       <c r="A132" t="s">
         <v>52</v>
       </c>
@@ -2020,12 +2001,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6">
       <c r="A133" t="s">
         <v>45</v>
       </c>
       <c r="B133">
-        <v>212.46523596919729</v>
+        <v>212.4652359691973</v>
       </c>
       <c r="C133" t="s">
         <v>1</v>
@@ -2037,12 +2018,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6">
       <c r="A134" t="s">
         <v>22</v>
       </c>
       <c r="B134">
-        <v>0.22639738259012829</v>
+        <v>0.2263973825901283</v>
       </c>
       <c r="C134" t="s">
         <v>23</v>
@@ -2054,12 +2035,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6">
       <c r="A135" t="s">
         <v>34</v>
       </c>
       <c r="B135">
-        <v>-2.114652359691974E-2</v>
+        <v>-0.02114652359691974</v>
       </c>
       <c r="C135" t="s">
         <v>1</v>
@@ -2071,7 +2052,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="137" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6">
       <c r="A137" s="1" t="s">
         <v>2</v>
       </c>
@@ -2079,7 +2060,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6">
       <c r="A138" t="s">
         <v>4</v>
       </c>
@@ -2087,7 +2068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6">
       <c r="A139" t="s">
         <v>5</v>
       </c>
@@ -2095,7 +2076,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6">
       <c r="A140" t="s">
         <v>6</v>
       </c>
@@ -2103,7 +2084,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6">
       <c r="A141" t="s">
         <v>7</v>
       </c>
@@ -2111,7 +2092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6">
       <c r="A142" t="s">
         <v>8</v>
       </c>
@@ -2119,7 +2100,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6">
       <c r="A143" t="s">
         <v>10</v>
       </c>
@@ -2127,12 +2108,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="144" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6">
       <c r="A144" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6">
       <c r="A145" t="s">
         <v>13</v>
       </c>
@@ -2152,7 +2133,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6">
       <c r="A146" t="s">
         <v>53</v>
       </c>
@@ -2169,7 +2150,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6">
       <c r="A147" t="s">
         <v>54</v>
       </c>
@@ -2186,12 +2167,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6">
       <c r="A148" t="s">
         <v>22</v>
       </c>
       <c r="B148">
-        <v>2.4863387978142082E-3</v>
+        <v>0.002486338797814208</v>
       </c>
       <c r="C148" t="s">
         <v>23</v>
@@ -2203,12 +2184,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6">
       <c r="A149" t="s">
         <v>34</v>
       </c>
       <c r="B149">
-        <v>-1.3333333333333331E-3</v>
+        <v>-0.001333333333333333</v>
       </c>
       <c r="C149" t="s">
         <v>1</v>
@@ -2220,7 +2201,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="151" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6">
       <c r="A151" s="1" t="s">
         <v>2</v>
       </c>
@@ -2228,7 +2209,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6">
       <c r="A152" t="s">
         <v>4</v>
       </c>
@@ -2236,7 +2217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6">
       <c r="A153" t="s">
         <v>5</v>
       </c>
@@ -2244,7 +2225,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6">
       <c r="A154" t="s">
         <v>6</v>
       </c>
@@ -2252,7 +2233,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6">
       <c r="A155" t="s">
         <v>7</v>
       </c>
@@ -2260,7 +2241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6">
       <c r="A156" t="s">
         <v>8</v>
       </c>
@@ -2268,7 +2249,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6">
       <c r="A157" t="s">
         <v>10</v>
       </c>
@@ -2276,12 +2257,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6">
       <c r="A158" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6">
       <c r="A159" t="s">
         <v>13</v>
       </c>
@@ -2301,7 +2282,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6">
       <c r="A160" t="s">
         <v>44</v>
       </c>
@@ -2318,12 +2299,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6">
       <c r="A161" t="s">
         <v>3</v>
       </c>
       <c r="B161">
-        <v>0.84602368866328259</v>
+        <v>0.8460236886632826</v>
       </c>
       <c r="C161" t="s">
         <v>1</v>
@@ -2335,12 +2316,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6">
       <c r="A162" t="s">
         <v>55</v>
       </c>
       <c r="B162">
-        <v>0.15397631133671741</v>
+        <v>0.1539763113367174</v>
       </c>
       <c r="C162" t="s">
         <v>1</v>
@@ -2352,7 +2333,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6">
       <c r="A163" t="s">
         <v>22</v>
       </c>
@@ -2369,7 +2350,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="165" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6">
       <c r="A165" s="1" t="s">
         <v>2</v>
       </c>
@@ -2377,7 +2358,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6">
       <c r="A166" t="s">
         <v>4</v>
       </c>
@@ -2385,7 +2366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6">
       <c r="A167" t="s">
         <v>5</v>
       </c>
@@ -2393,7 +2374,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6">
       <c r="A168" t="s">
         <v>6</v>
       </c>
@@ -2401,7 +2382,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6">
       <c r="A169" t="s">
         <v>7</v>
       </c>
@@ -2409,7 +2390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6">
       <c r="A170" t="s">
         <v>8</v>
       </c>
@@ -2417,7 +2398,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6">
       <c r="A171" t="s">
         <v>10</v>
       </c>
@@ -2425,12 +2406,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="172" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6">
       <c r="A172" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6">
       <c r="A173" t="s">
         <v>13</v>
       </c>
@@ -2450,12 +2431,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6">
       <c r="A174" t="s">
         <v>56</v>
       </c>
       <c r="B174">
-        <v>3.0901639344262289E-4</v>
+        <v>0.0003090163934426229</v>
       </c>
       <c r="D174" t="s">
         <v>11</v>
@@ -2467,7 +2448,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6">
       <c r="A175" t="s">
         <v>27</v>
       </c>
@@ -2484,7 +2465,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6">
       <c r="A176" t="s">
         <v>30</v>
       </c>
@@ -2501,7 +2482,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6">
       <c r="A177" t="s">
         <v>32</v>
       </c>
@@ -2518,7 +2499,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6">
       <c r="A178" t="s">
         <v>15</v>
       </c>
@@ -2535,7 +2516,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6">
       <c r="A179" t="s">
         <v>49</v>
       </c>
@@ -2552,7 +2533,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6">
       <c r="A180" t="s">
         <v>3</v>
       </c>
@@ -2569,7 +2550,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6">
       <c r="A181" t="s">
         <v>57</v>
       </c>
@@ -2586,12 +2567,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6">
       <c r="A182" t="s">
         <v>22</v>
       </c>
       <c r="B182">
-        <v>1.656513157894737E-4</v>
+        <v>0.0001656513157894737</v>
       </c>
       <c r="C182" t="s">
         <v>23</v>
@@ -2603,7 +2584,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6">
       <c r="A183" t="s">
         <v>59</v>
       </c>
@@ -2620,12 +2601,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6">
       <c r="A184" t="s">
         <v>60</v>
       </c>
       <c r="B184">
-        <v>9.0000000000000019E-5</v>
+        <v>9.000000000000002E-05</v>
       </c>
       <c r="C184" t="s">
         <v>40</v>
@@ -2637,7 +2618,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6">
       <c r="A185" t="s">
         <v>61</v>
       </c>
@@ -2654,12 +2635,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6">
       <c r="A186" t="s">
         <v>34</v>
       </c>
       <c r="B186">
-        <v>-5.0000000000000002E-5</v>
+        <v>-5E-05</v>
       </c>
       <c r="C186" t="s">
         <v>1</v>
@@ -2671,7 +2652,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6">
       <c r="A188" s="1" t="s">
         <v>2</v>
       </c>
@@ -2679,7 +2660,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6">
       <c r="A189" t="s">
         <v>4</v>
       </c>
@@ -2687,7 +2668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6">
       <c r="A190" t="s">
         <v>5</v>
       </c>
@@ -2695,7 +2676,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6">
       <c r="A191" t="s">
         <v>6</v>
       </c>
@@ -2703,7 +2684,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6">
       <c r="A192" t="s">
         <v>7</v>
       </c>
@@ -2711,7 +2692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6">
       <c r="A193" t="s">
         <v>8</v>
       </c>
@@ -2719,7 +2700,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6">
       <c r="A194" t="s">
         <v>10</v>
       </c>
@@ -2727,12 +2708,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6">
       <c r="A195" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6">
       <c r="A196" t="s">
         <v>13</v>
       </c>
@@ -2752,12 +2733,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6">
       <c r="A197" t="s">
         <v>62</v>
       </c>
       <c r="B197">
-        <v>-2.3000000000000001E-4</v>
+        <v>-0.00023</v>
       </c>
       <c r="D197" t="s">
         <v>11</v>
@@ -2769,12 +2750,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6">
       <c r="A198" t="s">
         <v>43</v>
       </c>
       <c r="B198">
-        <v>-1.6199999999999999E-3</v>
+        <v>-0.00162</v>
       </c>
       <c r="D198" t="s">
         <v>38</v>
@@ -2786,12 +2767,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6">
       <c r="A199" t="s">
         <v>64</v>
       </c>
       <c r="B199">
-        <v>-7.0000000000000007E-5</v>
+        <v>-7.000000000000001E-05</v>
       </c>
       <c r="D199" t="s">
         <v>11</v>
@@ -2803,7 +2784,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6">
       <c r="A200" t="s">
         <v>33</v>
       </c>
@@ -2820,12 +2801,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6">
       <c r="A201" t="s">
         <v>3</v>
       </c>
       <c r="B201">
-        <v>0.13750000000000001</v>
+        <v>0.1375</v>
       </c>
       <c r="C201" t="s">
         <v>1</v>
@@ -2837,7 +2818,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6">
       <c r="A202" t="s">
         <v>65</v>
       </c>
@@ -2854,12 +2835,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6">
       <c r="A203" t="s">
         <v>22</v>
       </c>
       <c r="B203">
-        <v>8.1999999999999987E-4</v>
+        <v>0.0008199999999999999</v>
       </c>
       <c r="C203" t="s">
         <v>23</v>
@@ -2871,12 +2852,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6">
       <c r="A204" t="s">
         <v>50</v>
       </c>
       <c r="B204">
-        <v>2.4000000000000001E-4</v>
+        <v>0.00024</v>
       </c>
       <c r="C204" t="s">
         <v>40</v>
@@ -2888,12 +2869,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6">
       <c r="A205" t="s">
         <v>66</v>
       </c>
       <c r="B205">
-        <v>1.2E-4</v>
+        <v>0.00012</v>
       </c>
       <c r="C205" t="s">
         <v>47</v>
@@ -2905,7 +2886,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="207" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6">
       <c r="A207" s="1" t="s">
         <v>2</v>
       </c>
@@ -2913,7 +2894,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6">
       <c r="A208" t="s">
         <v>4</v>
       </c>
@@ -2921,7 +2902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6">
       <c r="A209" t="s">
         <v>5</v>
       </c>
@@ -2929,7 +2910,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6">
       <c r="A210" t="s">
         <v>6</v>
       </c>
@@ -2937,7 +2918,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6">
       <c r="A211" t="s">
         <v>7</v>
       </c>
@@ -2945,7 +2926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6">
       <c r="A212" t="s">
         <v>8</v>
       </c>
@@ -2953,7 +2934,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6">
       <c r="A213" t="s">
         <v>10</v>
       </c>
@@ -2961,12 +2942,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="214" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6">
       <c r="A214" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6">
       <c r="A215" t="s">
         <v>13</v>
       </c>
@@ -2986,7 +2967,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6">
       <c r="A216" t="s">
         <v>43</v>
       </c>
@@ -3003,7 +2984,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6">
       <c r="A217" t="s">
         <v>67</v>
       </c>
@@ -3020,7 +3001,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6">
       <c r="A218" t="s">
         <v>53</v>
       </c>
@@ -3037,12 +3018,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6">
       <c r="A219" t="s">
         <v>37</v>
       </c>
       <c r="B219">
-        <v>0.35294117647058831</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="C219" t="s">
         <v>1</v>
@@ -3054,7 +3035,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6">
       <c r="A220" t="s">
         <v>22</v>
       </c>
@@ -3071,7 +3052,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="222" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6">
       <c r="A222" s="1" t="s">
         <v>2</v>
       </c>
@@ -3079,7 +3060,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6">
       <c r="A223" t="s">
         <v>4</v>
       </c>
@@ -3087,7 +3068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6">
       <c r="A224" t="s">
         <v>5</v>
       </c>
@@ -3095,7 +3076,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6">
       <c r="A225" t="s">
         <v>6</v>
       </c>
@@ -3103,7 +3084,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6">
       <c r="A226" t="s">
         <v>7</v>
       </c>
@@ -3111,7 +3092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6">
       <c r="A227" t="s">
         <v>8</v>
       </c>
@@ -3119,7 +3100,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6">
       <c r="A228" t="s">
         <v>10</v>
       </c>
@@ -3127,12 +3108,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="229" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6">
       <c r="A229" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6">
       <c r="A230" t="s">
         <v>13</v>
       </c>
@@ -3152,7 +3133,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6">
       <c r="A231" t="s">
         <v>65</v>
       </c>
@@ -3169,12 +3150,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6">
       <c r="A232" t="s">
         <v>35</v>
       </c>
       <c r="B232">
-        <v>2.2770000000000001</v>
+        <v>2.277</v>
       </c>
       <c r="C232" t="s">
         <v>1</v>
@@ -3186,7 +3167,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6">
       <c r="A233" t="s">
         <v>37</v>
       </c>
@@ -3203,12 +3184,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6">
       <c r="A234" t="s">
         <v>22</v>
       </c>
       <c r="B234">
-        <v>3.33219512195122E-3</v>
+        <v>0.00333219512195122</v>
       </c>
       <c r="C234" t="s">
         <v>23</v>
@@ -3220,12 +3201,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6">
       <c r="A235" t="s">
         <v>68</v>
       </c>
       <c r="B235">
-        <v>1.2500000000000001E-2</v>
+        <v>0.0125</v>
       </c>
       <c r="C235" t="s">
         <v>40</v>
@@ -3237,7 +3218,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="237" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6">
       <c r="A237" s="1" t="s">
         <v>2</v>
       </c>
@@ -3245,7 +3226,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6">
       <c r="A238" t="s">
         <v>4</v>
       </c>
@@ -3253,7 +3234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6">
       <c r="A239" t="s">
         <v>5</v>
       </c>
@@ -3261,7 +3242,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6">
       <c r="A240" t="s">
         <v>6</v>
       </c>
@@ -3269,7 +3250,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6">
       <c r="A241" t="s">
         <v>7</v>
       </c>
@@ -3277,7 +3258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6">
       <c r="A242" t="s">
         <v>8</v>
       </c>
@@ -3285,7 +3266,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6">
       <c r="A243" t="s">
         <v>10</v>
       </c>
@@ -3293,12 +3274,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="244" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6">
       <c r="A244" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6">
       <c r="A245" t="s">
         <v>13</v>
       </c>
@@ -3318,7 +3299,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6">
       <c r="A246" t="s">
         <v>54</v>
       </c>
@@ -3335,7 +3316,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6">
       <c r="A247" t="s">
         <v>3</v>
       </c>
@@ -3352,12 +3333,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6">
       <c r="A248" t="s">
         <v>51</v>
       </c>
       <c r="B248">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="C248" t="s">
         <v>1</v>
@@ -3369,12 +3350,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6">
       <c r="A249" t="s">
         <v>37</v>
       </c>
       <c r="B249">
-        <v>0.21954661057262259</v>
+        <v>0.2195466105726226</v>
       </c>
       <c r="C249" t="s">
         <v>1</v>
@@ -3386,7 +3367,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="251" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6">
       <c r="A251" s="1" t="s">
         <v>2</v>
       </c>
@@ -3394,7 +3375,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6">
       <c r="A252" t="s">
         <v>4</v>
       </c>
@@ -3402,7 +3383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6">
       <c r="A253" t="s">
         <v>5</v>
       </c>
@@ -3410,7 +3391,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6">
       <c r="A254" t="s">
         <v>6</v>
       </c>
@@ -3418,7 +3399,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6">
       <c r="A255" t="s">
         <v>7</v>
       </c>
@@ -3426,7 +3407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6">
       <c r="A256" t="s">
         <v>8</v>
       </c>
@@ -3434,7 +3415,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6">
       <c r="A257" t="s">
         <v>10</v>
       </c>
@@ -3442,12 +3423,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="258" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6">
       <c r="A258" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6">
       <c r="A259" t="s">
         <v>13</v>
       </c>
@@ -3467,7 +3448,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6">
       <c r="A260" t="s">
         <v>55</v>
       </c>
@@ -3484,7 +3465,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6">
       <c r="A261" t="s">
         <v>3</v>
       </c>
@@ -3501,12 +3482,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6">
       <c r="A262" t="s">
         <v>52</v>
       </c>
       <c r="B262">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="C262" t="s">
         <v>1</v>
@@ -3518,12 +3499,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6">
       <c r="A263" t="s">
         <v>37</v>
       </c>
       <c r="B263">
-        <v>0.21954661057262259</v>
+        <v>0.2195466105726226</v>
       </c>
       <c r="C263" t="s">
         <v>1</v>
@@ -3535,7 +3516,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="265" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6">
       <c r="A265" s="1" t="s">
         <v>2</v>
       </c>
@@ -3543,7 +3524,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6">
       <c r="A266" t="s">
         <v>4</v>
       </c>
@@ -3551,7 +3532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6">
       <c r="A267" t="s">
         <v>5</v>
       </c>
@@ -3559,7 +3540,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6">
       <c r="A268" t="s">
         <v>6</v>
       </c>
@@ -3567,7 +3548,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6">
       <c r="A269" t="s">
         <v>7</v>
       </c>
@@ -3575,7 +3556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6">
       <c r="A270" t="s">
         <v>8</v>
       </c>
@@ -3583,7 +3564,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6">
       <c r="A271" t="s">
         <v>10</v>
       </c>
@@ -3591,12 +3572,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="272" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6">
       <c r="A272" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6">
       <c r="A273" t="s">
         <v>13</v>
       </c>
@@ -3616,7 +3597,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6">
       <c r="A274" t="s">
         <v>15</v>
       </c>
@@ -3633,7 +3614,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6">
       <c r="A275" t="s">
         <v>34</v>
       </c>
@@ -3650,7 +3631,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6">
       <c r="A276" t="s">
         <v>69</v>
       </c>
